--- a/CYP1A2_Allele_def_rs_excluidos.xlsx
+++ b/CYP1A2_Allele_def_rs_excluidos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="107">
   <si>
     <t>rsID</t>
   </si>
@@ -274,9 +274,6 @@
     <t>https://gnomad.broadinstitute.org/variant/15-74749838-CG-C?dataset=gnomad_r4</t>
   </si>
   <si>
-    <t>rs</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
@@ -332,6 +329,18 @@
   </si>
   <si>
     <t>MAF European (non-finnish)</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenomAD </t>
+  </si>
+  <si>
+    <t>Base de datos</t>
+  </si>
+  <si>
+    <t>rs/*alelo</t>
   </si>
 </sst>
 </file>
@@ -363,7 +372,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -373,6 +382,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -399,6 +414,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1175,10 +1191,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="28" max="28" width="11.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,21 +1274,24 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1346,7 +1368,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1360,21 +1382,24 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
       <c r="T5" t="s">
         <v>27</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1388,10 +1413,13 @@
         <v>8.2949999999999997E-5</v>
       </c>
       <c r="AB6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1405,10 +1433,13 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1422,10 +1453,13 @@
         <v>1.3560000000000001E-5</v>
       </c>
       <c r="AB8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1439,10 +1473,13 @@
         <v>1.6950000000000001E-6</v>
       </c>
       <c r="AB9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1455,11 +1492,14 @@
       <c r="AA10">
         <v>0</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AB10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC10" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1473,10 +1513,13 @@
         <v>4.5970000000000002E-5</v>
       </c>
       <c r="AB11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -1490,10 +1533,13 @@
         <v>1.9490000000000001E-5</v>
       </c>
       <c r="AB12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1507,10 +1553,13 @@
         <v>1.102E-5</v>
       </c>
       <c r="AB13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1524,10 +1573,13 @@
         <v>9.3219999999999999E-6</v>
       </c>
       <c r="AB14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1541,10 +1593,13 @@
         <v>2.7209999999999999E-5</v>
       </c>
       <c r="AB15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -1558,10 +1613,13 @@
         <v>4.6529999999999998E-4</v>
       </c>
       <c r="AB16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -1575,10 +1633,13 @@
         <v>8.1950000000000002E-4</v>
       </c>
       <c r="AB17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -1592,10 +1653,13 @@
         <v>3.7289999999999997E-5</v>
       </c>
       <c r="AB18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -1609,10 +1673,13 @@
         <v>0</v>
       </c>
       <c r="AB19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -1626,10 +1693,13 @@
         <v>4.2370000000000003E-6</v>
       </c>
       <c r="AB20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1643,10 +1713,13 @@
         <v>2.9920000000000001E-4</v>
       </c>
       <c r="AB21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -1660,10 +1733,13 @@
         <v>0</v>
       </c>
       <c r="AB22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -1677,10 +1753,13 @@
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -1694,10 +1773,13 @@
         <v>0</v>
       </c>
       <c r="AB24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -1711,10 +1793,13 @@
         <v>1.697E-6</v>
       </c>
       <c r="AB25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -1728,10 +1813,13 @@
         <v>2.2030000000000001E-5</v>
       </c>
       <c r="AB26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -1745,12 +1833,24 @@
         <v>1.6950000000000001E-6</v>
       </c>
       <c r="AB27" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z28" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA28">
+        <f>SUM(AA4:AA27)*100</f>
+        <v>0.18621659999999998</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AB10" r:id="rId1"/>
+    <hyperlink ref="AC10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
